--- a/Notes and data for listed articles/(row 3) data for 2023 Chen et al./raw_data/data_for_platform_num_crossed.xlsx
+++ b/Notes and data for listed articles/(row 3) data for 2023 Chen et al./raw_data/data_for_platform_num_crossed.xlsx
@@ -93,7 +93,7 @@
     <xdr:ext cx="3905250" cy="2362200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -121,7 +121,7 @@
     <xdr:ext cx="3371850" cy="2571750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
